--- a/parafit_summary_medium.xlsx
+++ b/parafit_summary_medium.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,67 +485,89 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Coala_Medium</t>
+          <t>Asymmetree_Medium</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2520990.82</v>
+        <v>3518.51</v>
       </c>
       <c r="C3" t="n">
-        <v>6042851.53</v>
+        <v>3365.82</v>
       </c>
       <c r="D3" t="n">
-        <v>500</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>402</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>80.40000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Real_Data</t>
+          <t>Coala_Medium</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15807.72</v>
+        <v>2520990.82</v>
       </c>
       <c r="C4" t="n">
-        <v>21682.83</v>
+        <v>6042851.53</v>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>402</v>
       </c>
       <c r="F4" t="n">
-        <v>60.87</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>Real_Data</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>15807.72</v>
+      </c>
+      <c r="C5" t="n">
+        <v>21682.83</v>
+      </c>
+      <c r="D5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" t="n">
+        <v>56.52</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
           <t>Treeducken_Medium</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B6" t="n">
         <v>1196.33</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C6" t="n">
         <v>2776.97</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>489</v>
       </c>
-      <c r="E5" t="n">
-        <v>299</v>
-      </c>
-      <c r="F5" t="n">
-        <v>61.15</v>
+      <c r="E6" t="n">
+        <v>301</v>
+      </c>
+      <c r="F6" t="n">
+        <v>61.55</v>
       </c>
     </row>
   </sheetData>
